--- a/keamanan_sistem_informasi/Latihan_STRIDE_DREAD_1_backup.xlsx
+++ b/keamanan_sistem_informasi/Latihan_STRIDE_DREAD_1_backup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\FindServices\keamanan_sistem_informasi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5026111-9767-4EB7-9DB8-F7B847E45B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CCE725-A0B6-4E55-9A11-00803389C6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -883,10 +883,9 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -903,27 +902,15 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF9DC3E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -973,6 +960,19 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF9DC3E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1559,16 +1559,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="34"/>
+      <c r="C2" s="41"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="35"/>
+      <c r="C3" s="42"/>
     </row>
     <row r="5" spans="2:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
@@ -1686,78 +1686,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39" t="s">
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="40" t="s">
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="41" t="s">
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
       <c r="S3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1821,14 +1821,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="34" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="34" t="s">
         <v>143</v>
       </c>
       <c r="D5" s="14"/>
@@ -1876,14 +1876,14 @@
       </c>
       <c r="S5" s="13"/>
     </row>
-    <row r="6" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>2</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="34" t="s">
         <v>145</v>
       </c>
       <c r="D6" s="14"/>
@@ -1931,14 +1931,14 @@
       </c>
       <c r="S6" s="13"/>
     </row>
-    <row r="7" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="34" t="s">
         <v>147</v>
       </c>
       <c r="D7" s="14">
@@ -1986,14 +1986,14 @@
       </c>
       <c r="S7" s="13"/>
     </row>
-    <row r="8" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>4</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="34" t="s">
         <v>149</v>
       </c>
       <c r="D8" s="14"/>
@@ -2041,14 +2041,14 @@
       </c>
       <c r="S8" s="13"/>
     </row>
-    <row r="9" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="66" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>5</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="34" t="s">
         <v>155</v>
       </c>
       <c r="D9" s="14"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="12">
-        <f>IF(COUNT(D9:I9)=0,"",SUM(D9:I9))</f>
+        <f t="shared" ref="J9:J14" si="3">IF(COUNT(D9:I9)=0,"",SUM(D9:I9))</f>
         <v>1</v>
       </c>
       <c r="K9" s="14">
@@ -2092,14 +2092,14 @@
       </c>
       <c r="S9" s="13"/>
     </row>
-    <row r="10" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="66" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
         <v>6</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="34" t="s">
         <v>156</v>
       </c>
       <c r="D10" s="14">
@@ -2117,7 +2117,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="12">
-        <f>IF(COUNT(D10:I10)=0,"",SUM(D10:I10))</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="K10" s="14">
@@ -2149,14 +2149,14 @@
       </c>
       <c r="S10" s="13"/>
     </row>
-    <row r="11" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="66" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
         <v>7</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="34" t="s">
         <v>157</v>
       </c>
       <c r="D11" s="14">
@@ -2172,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="12">
-        <f>IF(COUNT(D11:I11)=0,"",SUM(D11:I11))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="K11" s="14">
@@ -2204,14 +2204,14 @@
       </c>
       <c r="S11" s="13"/>
     </row>
-    <row r="12" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
         <v>8</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="34" t="s">
         <v>158</v>
       </c>
       <c r="D12" s="14">
@@ -2227,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="12">
-        <f>IF(COUNT(D12:I12)=0,"",SUM(D12:I12))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="K12" s="14">
@@ -2259,14 +2259,14 @@
       </c>
       <c r="S12" s="13"/>
     </row>
-    <row r="13" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
         <v>9</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="34" t="s">
         <v>159</v>
       </c>
       <c r="D13" s="14">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="12">
-        <f>IF(COUNT(D13:I13)=0,"",SUM(D13:I13))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="K13" s="14">
@@ -2318,8 +2318,8 @@
       <c r="A14" s="12">
         <v>10</v>
       </c>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
@@ -2327,7 +2327,7 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="12" t="str">
-        <f>IF(COUNT(D14:I14)=0,"",SUM(D14:I14))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K14" s="14"/>
@@ -3410,7 +3410,7 @@
     <mergeCell ref="P3:R3"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:I44">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3425,16 +3425,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q44">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"CRITICAL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"HIGH"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"MEDIUM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"LOW"</formula>
     </cfRule>
   </conditionalFormatting>
